--- a/Wikidata Delta/lt_gen_excels/pep_lithuania_living_relevant_rca_lookup.xlsx
+++ b/Wikidata Delta/lt_gen_excels/pep_lithuania_living_relevant_rca_lookup.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="195">
   <si>
     <r>
       <rPr>
@@ -29,6 +29,14 @@
         <b/>
       </rPr>
       <t>RCA ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
   </si>
   <si>
@@ -768,787 +776,811 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr defaultRowHeight="12.8" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.53515625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.51" customWidth="1"/>
     <col min="2" max="2" width="24.67" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" ht="12.8" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B58" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B59" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B60" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B63" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B64" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B67" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B68" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B69" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B70" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B71" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="73" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B73" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B74" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B75" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="78" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B78" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="79" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B81" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B82" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B83" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="84" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B84" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="85" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B85" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="86" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="87" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B87" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="89" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B89" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B90" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="91" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B91" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B92" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="93" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B93" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B95" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B96" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" ht="12.8" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B97" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
